--- a/data/trans_orig/P79$hipoteca_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79$hipoteca_2023-Edad-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>38195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22575</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42255</t>
+          <t>46928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26547</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1480</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27991</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1527</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>17102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>21227</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50513</t>
+          <t>58604</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31175</t>
+          <t>35296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65189</t>
+          <t>71104</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>87240</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>53725</t>
+          <t>64831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>118550</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>10027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>34702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23985</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43354</t>
+          <t>50592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>330860</t>
+          <t>324045</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306582</t>
+          <t>298199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345906</t>
+          <t>342301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>235562</t>
+          <t>274398</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>213917</t>
+          <t>251810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>251475</t>
+          <t>292362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>566422</t>
+          <t>598443</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535571</t>
+          <t>566087</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>590741</t>
+          <t>625474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>29771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24133</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15380</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>889</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2794</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1228</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>20991</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17569</t>
+          <t>21913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>60397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>78948</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52175</t>
+          <t>61715</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86992</t>
+          <t>101825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>975</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>25825</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16087</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42584</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11839</t>
+          <t>14885</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25106</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54229</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>356444</t>
+          <t>401778</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>333526</t>
+          <t>382519</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>369816</t>
+          <t>419473</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>364947</t>
+          <t>408727</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>348266</t>
+          <t>390436</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>379088</t>
+          <t>423694</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>721391</t>
+          <t>810505</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>696289</t>
+          <t>782382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>742351</t>
+          <t>834972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -3219,67 +3219,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8453</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15372</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>9062</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>15239</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>8237</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3859</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>14394</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,17 +3289,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>11778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26274</t>
+          <t>28875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20119</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>19474</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>29869</t>
+          <t>40262</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11751</t>
+          <t>16162</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>24081</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>32806</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>45428</t>
+          <t>60148</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>13487</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,22 +3480,22 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6297</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,32 +3593,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>824</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -3671,32 +3671,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,22 +3741,22 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7984</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>23286</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -3784,67 +3784,67 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43443</t>
+          <t>54722</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>9,12%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>46255</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>36172</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>58893</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>27029</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>50362</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>85265</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85719</t>
+          <t>103055</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -3897,22 +3897,22 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,17 +3967,17 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4133,12 +4133,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>5644</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4158,32 +4158,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>33721</t>
+          <t>39991</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>26971</t>
+          <t>31609</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>54957</t>
+          <t>64240</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>445775</t>
+          <t>507502</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>428602</t>
+          <t>487184</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>462010</t>
+          <t>524383</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>509212</t>
+          <t>524359</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>493785</t>
+          <t>507742</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>527433</t>
+          <t>536908</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>954987</t>
+          <t>1031861</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>931190</t>
+          <t>1006917</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>978120</t>
+          <t>1054938</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>22317</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>19204</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>30926</t>
+          <t>38838</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13865</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>19741</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4805,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9783</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,32 +4840,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1423</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>15929</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>18254</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28092</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>56419</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>77177</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>41480</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>73625</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>117934</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>60026</t>
+          <t>100848</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>129485</t>
+          <t>138338</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -5144,32 +5144,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,32 +5179,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13141</t>
+          <t>14130</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>21103</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>46987</t>
+          <t>46505</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>15283</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>51931</t>
+          <t>59958</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>31302</t>
+          <t>46897</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>69324</t>
+          <t>75617</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>789054</t>
+          <t>583278</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>746587</t>
+          <t>560277</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>837743</t>
+          <t>602218</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>611763</t>
+          <t>619711</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>596953</t>
+          <t>604564</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>627946</t>
+          <t>633606</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1400818</t>
+          <t>1202989</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1360430</t>
+          <t>1178099</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1469829</t>
+          <t>1226746</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -5713,32 +5713,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13053</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,32 +5748,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5861,32 +5861,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5939,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5974,22 +5974,22 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6009,17 +6009,17 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6122,32 +6122,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>8267</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>23487</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,32 +6200,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,17 +6235,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>14621</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>28781</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -6278,32 +6278,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>42103</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>75005</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6313,32 +6313,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>55583</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>71142</t>
+          <t>80300</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>111849</t>
+          <t>128078</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>94577</t>
+          <t>109141</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>128583</t>
+          <t>148566</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -6391,32 +6391,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>4357</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>11474</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -6730,32 +6730,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>29996</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>21425</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>27444</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>38261</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>51364</t>
+          <t>57440</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>40398</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>64125</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>466364</t>
+          <t>502094</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>450763</t>
+          <t>482535</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>480545</t>
+          <t>517224</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>445855</t>
+          <t>493647</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>431226</t>
+          <t>478734</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>457684</t>
+          <t>506438</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>912218</t>
+          <t>995741</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>891668</t>
+          <t>972838</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>932174</t>
+          <t>1017370</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -6960,32 +6960,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7030,32 +7030,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7108,32 +7108,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>882</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7143,32 +7143,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4048</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>606</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>585</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -7412,32 +7412,32 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7447,32 +7447,32 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7482,32 +7482,32 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -7525,32 +7525,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>37820</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>25520</t>
+          <t>29279</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>47822</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7560,32 +7560,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>32726</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>60369</t>
+          <t>51623</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7595,32 +7595,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>66502</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>96871</t>
+          <t>93405</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>612</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>612</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -7977,32 +7977,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>19151</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8012,32 +8012,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>27486</t>
+          <t>25051</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8047,32 +8047,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>28094</t>
+          <t>31537</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>41639</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -8090,32 +8090,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>317529</t>
+          <t>349417</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>308075</t>
+          <t>337546</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>326646</t>
+          <t>358892</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>549682</t>
+          <t>372927</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>520935</t>
+          <t>362014</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>579860</t>
+          <t>383106</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>867211</t>
+          <t>722343</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>835845</t>
+          <t>707490</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>912629</t>
+          <t>736791</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8320,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8355,32 +8355,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8390,17 +8390,17 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8410,12 +8410,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>596</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8503,17 +8503,17 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -8659,32 +8659,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8694,32 +8694,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8729,17 +8729,17 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>11660</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -8772,32 +8772,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>21750</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8807,32 +8807,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>28214</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8842,32 +8842,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>60093</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>74454</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -9224,32 +9224,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9259,32 +9259,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>14491</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>26716</t>
+          <t>30958</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>28052</t>
+          <t>31529</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>23662</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>36484</t>
+          <t>41215</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -9337,32 +9337,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>247863</t>
+          <t>271517</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>239276</t>
+          <t>262407</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>254800</t>
+          <t>279426</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,32 +9372,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>357300</t>
+          <t>386448</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>347687</t>
+          <t>375643</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>366530</t>
+          <t>396966</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>605164</t>
+          <t>657965</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>592731</t>
+          <t>643589</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>617929</t>
+          <t>669700</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -9454,32 +9454,32 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>48897</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9489,32 +9489,32 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>31908</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9524,32 +9524,32 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>40136</t>
+          <t>46623</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>68994</t>
+          <t>77646</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -9567,32 +9567,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>34323</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>65621</t>
+          <t>85539</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9602,32 +9602,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>48871</t>
+          <t>67680</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>87640</t>
+          <t>105514</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9637,32 +9637,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>90124</t>
+          <t>125300</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>146012</t>
+          <t>178156</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -9680,32 +9680,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9715,32 +9715,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>10409</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>25731</t>
+          <t>26817</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9750,32 +9750,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>29981</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>58984</t>
+          <t>61950</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -9793,17 +9793,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>34800</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9828,17 +9828,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>20779</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -9863,17 +9863,17 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>18920</t>
+          <t>20573</t>
         </is>
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>46701</t>
+          <t>49566</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -9906,32 +9906,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>59263</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9941,32 +9941,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>53784</t>
+          <t>58000</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9976,32 +9976,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>75265</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>100895</t>
+          <t>114533</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -10019,32 +10019,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>195743</t>
+          <t>261531</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>289261</t>
+          <t>331263</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10054,32 +10054,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>252569</t>
+          <t>322238</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>344051</t>
+          <t>385949</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>481189</t>
+          <t>599265</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>618283</t>
+          <t>697938</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -10132,32 +10132,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10167,67 +10167,67 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>4189</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>21264</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>13530</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>33057</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="Q87" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R87" s="2" t="inlineStr">
-        <is>
-          <t>19206</t>
-        </is>
-      </c>
-      <c r="S87" s="2" t="inlineStr">
-        <is>
-          <t>11330</t>
-        </is>
-      </c>
-      <c r="T87" s="2" t="inlineStr">
-        <is>
-          <t>29347</t>
-        </is>
-      </c>
-      <c r="U87" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V87" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -10280,22 +10280,22 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>13268</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10315,22 +10315,22 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10393,67 +10393,67 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
           <t>0,03%</t>
         </is>
       </c>
-      <c r="P89" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q89" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R89" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="S89" s="2" t="inlineStr">
-        <is>
-          <t>1725</t>
-        </is>
-      </c>
-      <c r="T89" s="2" t="inlineStr">
-        <is>
-          <t>9292</t>
-        </is>
-      </c>
-      <c r="U89" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V89" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -10471,32 +10471,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>135957</t>
+          <t>157607</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>102394</t>
+          <t>128918</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>164376</t>
+          <t>188128</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10506,32 +10506,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>144951</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>103192</t>
+          <t>124725</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>149760</t>
+          <t>167612</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10541,32 +10541,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>261860</t>
+          <t>302558</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>226127</t>
+          <t>271095</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>303138</t>
+          <t>340065</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -10584,32 +10584,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>2953890</t>
+          <t>2939631</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2895118</t>
+          <t>2894495</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>3042585</t>
+          <t>2985086</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10619,32 +10619,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>3074321</t>
+          <t>3080217</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>3028389</t>
+          <t>3039780</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3148028</t>
+          <t>3117324</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10654,32 +10654,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>6028210</t>
+          <t>6019848</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>5945894</t>
+          <t>5961646</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>6138405</t>
+          <t>6077518</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
